--- a/artfynd/A 61045-2023 artfynd.xlsx
+++ b/artfynd/A 61045-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61045-2023 artfynd.xlsx
+++ b/artfynd/A 61045-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55713265</v>
+        <v>66538574</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,26 +708,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sunnerstetjärn Öster om, Vrm</t>
+          <t>Svenskmyrarna, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>342793.8697822151</v>
+        <v>342861</v>
       </c>
       <c r="R2" t="n">
-        <v>6603834.613982104</v>
+        <v>6603936</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-04-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Använt bohål i gran. Några år gammalt.</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +761,20 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>21375</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -806,12 +784,7 @@
         <v>66538596</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>342860.6811007226</v>
+        <v>342861</v>
       </c>
       <c r="R3" t="n">
-        <v>6603936.39573933</v>
+        <v>6603936</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,19 +853,9 @@
           <t>2012-05-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66538574</v>
+        <v>55713265</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,19 +920,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svenskmyrarna, Vrm</t>
+          <t>Sunnerstetjärn Öster om, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>342860.6811007226</v>
+        <v>342794</v>
       </c>
       <c r="R4" t="n">
-        <v>6603936.39573933</v>
+        <v>6603835</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,22 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Använt bohål i gran. Några år gammalt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,20 +985,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>21375</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
